--- a/brands.xlsx
+++ b/brands.xlsx
@@ -728,12 +728,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>images/brands/sicam/logo.png</t>
+          <t>images/brands/sicam/logo-clean.png</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>images/brands/sicam/tyre-changer.png</t>
+          <t>images/brands/sicam/hero-banner.jpg</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -813,7 +813,11 @@
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>images/brands/raasm/hero-banner.jpg</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>#1d00f4</t>
@@ -891,7 +895,11 @@
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>images/brands/kzubr/hero-banner.jpg</t>
+        </is>
+      </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
           <t>#ff6b00</t>
@@ -965,7 +973,11 @@
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>images/brands/maekida/hero-banner.jpg</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>#00b4d8</t>
@@ -1039,7 +1051,11 @@
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>images/brands/matika/hero-banner.jpg</t>
+        </is>
+      </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>#e63946</t>
@@ -1113,7 +1129,11 @@
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>images/brands/mega/hero-banner.jpg</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>#f4a261</t>
@@ -1187,7 +1207,11 @@
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>images/brands/miga/hero-banner.jpg</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>#2d6a4f</t>
@@ -1261,7 +1285,11 @@
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>images/brands/parksit/hero-banner.jpg</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>#457b9d</t>
@@ -1335,7 +1363,11 @@
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>images/brands/sharp/hero-banner.jpg</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
           <t>#c1121f</t>
@@ -1409,7 +1441,11 @@
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>images/brands/dunko/hero-banner.jpg</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>#6a0572</t>
